--- a/output/pdf_financials_xlsx/CSW.A.xlsx
+++ b/output/pdf_financials_xlsx/CSW.A.xlsx
@@ -879,13 +879,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>1.649</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.537</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>1.288</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>0</v>
@@ -1584,13 +1584,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>44.449</v>
+        <v>42.8</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>31.482</v>
+        <v>30.945</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>40.839</v>
+        <v>39.551</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>60.202</v>
@@ -1670,13 +1670,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>44.449</v>
+        <v>42.8</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>31.482</v>
+        <v>30.945</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>47.063</v>
+        <v>45.775</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>65.89</v>
@@ -1713,13 +1713,13 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>29.12931215266855</v>
+        <v>28.04865261612666</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>21.40962691946738</v>
+        <v>21.04443507473852</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>29.49437850168583</v>
+        <v>28.68718900016295</v>
       </c>
       <c r="E30" s="3" t="n">
         <v>44.90071279626021</v>
@@ -32578,7 +32578,7 @@
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
@@ -34260,7 +34260,7 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E376" s="5" t="n">

--- a/output/pdf_financials_xlsx/CSW.A.xlsx
+++ b/output/pdf_financials_xlsx/CSW.A.xlsx
@@ -952,10 +952,10 @@
         <v>-0</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>-0</v>
+        <v>-1.611</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>-0</v>
+        <v>0.074</v>
       </c>
     </row>
     <row r="14">
@@ -1614,10 +1614,10 @@
         <v>30.038</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>32.896</v>
+        <v>34.507</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>38.115</v>
+        <v>38.041</v>
       </c>
     </row>
     <row r="28">
@@ -1700,10 +1700,10 @@
         <v>30.038</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>32.896</v>
+        <v>34.507</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>38.115</v>
+        <v>38.041</v>
       </c>
     </row>
     <row r="30">
@@ -5317,30 +5317,28 @@
         <v>0</v>
       </c>
       <c r="D112" s="3" t="n">
-        <v>0</v>
+        <v>0.077</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>0</v>
+        <v>0.335</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>0</v>
+        <v>0.51</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>0</v>
+        <v>0.385</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="I112" s="3" t="n">
-        <v>0</v>
+        <v>0.616</v>
       </c>
       <c r="J112" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.032</v>
+      </c>
+      <c r="K112" s="3" t="n">
+        <v>0.271</v>
       </c>
       <c r="L112" s="1" t="inlineStr">
         <is>
@@ -15982,7 +15980,11 @@
           <t>Loss on disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr"/>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E131" t="inlineStr">
         <is>
           <t>-</t>
@@ -16622,7 +16624,11 @@
           <t>Addi:ons to intangible assets 13</t>
         </is>
       </c>
-      <c r="D140" t="inlineStr"/>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E140" t="inlineStr">
         <is>
           <t>-</t>
@@ -16696,7 +16702,11 @@
           <t>Proceeds from disposi:on of property and equipment</t>
         </is>
       </c>
-      <c r="D141" t="inlineStr"/>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E141" t="inlineStr">
         <is>
           <t>-</t>
@@ -18038,7 +18048,11 @@
           <t>Additions to intangible assets 13</t>
         </is>
       </c>
-      <c r="D159" t="inlineStr"/>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E159" t="inlineStr">
         <is>
           <t>-</t>
@@ -18112,7 +18126,11 @@
           <t>Proceeds from disposition of property and equipment</t>
         </is>
       </c>
-      <c r="D160" t="inlineStr"/>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E160" t="inlineStr">
         <is>
           <t>-</t>
@@ -19390,7 +19408,11 @@
           <t>Additions to intangible assets</t>
         </is>
       </c>
-      <c r="D177" t="inlineStr"/>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E177" t="inlineStr">
         <is>
           <t>-</t>
@@ -19466,7 +19488,11 @@
           <t>Proceeds from disposition of property and equipment</t>
         </is>
       </c>
-      <c r="D178" t="inlineStr"/>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E178" t="inlineStr">
         <is>
           <t>-</t>
@@ -20392,7 +20418,11 @@
           <t>Additions to intangible assets 14</t>
         </is>
       </c>
-      <c r="D190" t="inlineStr"/>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E190" t="inlineStr">
         <is>
           <t>-</t>
@@ -25624,7 +25654,11 @@
           <t>Net financial expense 25 8,021 7,840</t>
         </is>
       </c>
-      <c r="D258" t="inlineStr"/>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E258" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/CSW.A.xlsx
+++ b/output/pdf_financials_xlsx/CSW.A.xlsx
@@ -836,34 +836,34 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>71.91</v>
+        <v>43.405</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>62.442</v>
+        <v>43.025</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>87.913</v>
+        <v>40.456</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>85.861</v>
+        <v>58.851</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>83.09999999999999</v>
+        <v>37.043</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>88.306</v>
+        <v>33.46</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>83.029</v>
+        <v>27.239</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>97.708</v>
+        <v>41.487</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>96.13800000000001</v>
+        <v>32.67</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>94.11499999999999</v>
+        <v>28.34</v>
       </c>
       <c r="L11" s="3" t="n">
         <v>0</v>
@@ -1081,10 +1081,10 @@
         <v>30.038</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>32.896</v>
+        <v>23.333</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>38.115</v>
+        <v>27.453</v>
       </c>
     </row>
     <row r="17">
@@ -1124,10 +1124,10 @@
         <v>8.079000000000001</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>-8.987</v>
+        <v>0.576</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>-10.688</v>
+        <v>-0.026</v>
       </c>
     </row>
     <row r="18">
@@ -1614,10 +1614,10 @@
         <v>30.038</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>34.507</v>
+        <v>24.944</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>38.041</v>
+        <v>27.379</v>
       </c>
     </row>
     <row r="28">
@@ -1700,10 +1700,10 @@
         <v>30.038</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>34.507</v>
+        <v>24.944</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>38.041</v>
+        <v>27.379</v>
       </c>
     </row>
     <row r="30">
@@ -1790,10 +1790,10 @@
         <v>26.89593181969505</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>27.31943093385214</v>
+        <v>2.468606694381348</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>28.04145349599895</v>
+        <v>0.09470731796160711</v>
       </c>
     </row>
     <row r="32">
@@ -2121,10 +2121,10 @@
         <v>0</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>0</v>
+        <v>1.391</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>0</v>
+        <v>0.037</v>
       </c>
       <c r="F40" s="3" t="n">
         <v>0</v>
@@ -2164,10 +2164,10 @@
         <v>28.34</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>32.805</v>
+        <v>34.196</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>29.811</v>
+        <v>29.848</v>
       </c>
       <c r="F41" s="3" t="n">
         <v>25.725</v>
@@ -2465,10 +2465,10 @@
         <v>77.306</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>97.167</v>
+        <v>95.776</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>110.068</v>
+        <v>110.031</v>
       </c>
       <c r="F48" s="3" t="n">
         <v>109.069</v>
@@ -5120,7 +5120,7 @@
         <v>0</v>
       </c>
       <c r="C108" s="3" t="n">
-        <v>0</v>
+        <v>11.51</v>
       </c>
       <c r="D108" s="3" t="n">
         <v>0</v>
@@ -5141,7 +5141,7 @@
         <v>0</v>
       </c>
       <c r="J108" s="3" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="K108" s="1" t="inlineStr">
         <is>
@@ -5317,22 +5317,22 @@
         <v>0</v>
       </c>
       <c r="D112" s="3" t="n">
-        <v>0.077</v>
+        <v>0</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>0.335</v>
+        <v>0</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>0.51</v>
+        <v>0</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>0.385</v>
+        <v>0</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="I112" s="3" t="n">
-        <v>0.616</v>
+        <v>0</v>
       </c>
       <c r="J112" s="3" t="n">
         <v>0.032</v>
@@ -15904,7 +15904,11 @@
           <t>Impairment charge 13</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr"/>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>AssetImpairmentCharge</t>
+        </is>
+      </c>
       <c r="E130" t="inlineStr">
         <is>
           <t>-</t>
@@ -17686,7 +17690,11 @@
           <t>Impairment charge 14</t>
         </is>
       </c>
-      <c r="D154" t="inlineStr"/>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>AssetImpairmentCharge</t>
+        </is>
+      </c>
       <c r="E154" t="inlineStr">
         <is>
           <t>-</t>
@@ -18126,11 +18134,7 @@
           <t>Proceeds from disposition of property and equipment</t>
         </is>
       </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>SaleOfPPE</t>
-        </is>
-      </c>
+      <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr">
         <is>
           <t>-</t>
@@ -19488,11 +19492,7 @@
           <t>Proceeds from disposition of property and equipment</t>
         </is>
       </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>SaleOfPPE</t>
-        </is>
-      </c>
+      <c r="D178" t="inlineStr"/>
       <c r="E178" t="inlineStr">
         <is>
           <t>-</t>
@@ -22812,7 +22812,11 @@
           <t>Impairment charge (Note 17)</t>
         </is>
       </c>
-      <c r="D221" t="inlineStr"/>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>AssetImpairmentCharge</t>
+        </is>
+      </c>
       <c r="E221" t="inlineStr">
         <is>
           <t>-</t>
@@ -22962,7 +22966,11 @@
           <t>Future income taxes</t>
         </is>
       </c>
-      <c r="D223" t="inlineStr"/>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E223" s="5" t="n">
         <v>0.793</v>
       </c>
@@ -24344,7 +24352,11 @@
           <t>Impairment charge (Note 4)</t>
         </is>
       </c>
-      <c r="D241" t="inlineStr"/>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>AssetImpairmentCharge</t>
+        </is>
+      </c>
       <c r="E241" t="inlineStr">
         <is>
           <t>-</t>
@@ -25580,7 +25592,11 @@
           <t>Amortization and depreciation 27 16,278 15,443 Income tax recovery (expense) 19</t>
         </is>
       </c>
-      <c r="D257" t="inlineStr"/>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E257" t="inlineStr">
         <is>
           <t>-</t>
@@ -28086,7 +28102,11 @@
           <t>Earnings from operaAons</t>
         </is>
       </c>
-      <c r="D291" t="inlineStr"/>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
       <c r="E291" t="inlineStr">
         <is>
           <t>-</t>
@@ -29190,7 +29210,11 @@
           <t>Earnings from operations</t>
         </is>
       </c>
-      <c r="D307" t="inlineStr"/>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
       <c r="E307" t="inlineStr">
         <is>
           <t>-</t>
@@ -29684,7 +29708,11 @@
           <t>EARNINGS FROM OPERATIONS</t>
         </is>
       </c>
-      <c r="D314" t="inlineStr"/>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
       <c r="E314" t="inlineStr">
         <is>
           <t>-</t>
@@ -32384,7 +32412,11 @@
           <t>EARNINGS FROM OPERATIONS</t>
         </is>
       </c>
-      <c r="D351" t="inlineStr"/>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
       <c r="E351" t="inlineStr">
         <is>
           <t>-</t>
@@ -34142,7 +34174,11 @@
           <t>eaRNINgS fROM OPeRatIONS</t>
         </is>
       </c>
-      <c r="D374" t="inlineStr"/>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
       <c r="E374" s="5" t="n">
         <v>43.405</v>
       </c>
